--- a/PRISM_ROI_Calculator.xlsx
+++ b/PRISM_ROI_Calculator.xlsx
@@ -1,13 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_904627ABFFDFBA709314BC347F128F55D7276CC0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B0C6AF0-E9BD-46B0-A6A9-D8079CAC8759}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ROI Calculator" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Pricing Comparison" state="visible" r:id="rId5"/>
+    <sheet name="ROI Calculator" sheetId="1" r:id="rId1"/>
+    <sheet name="Pricing Comparison" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -317,76 +334,91 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="£#,##0"/>
+    <numFmt numFmtId="164" formatCode="\£#,##0"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;%&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0&quot; months&quot;"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF005F8C"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color rgb="FF005F8C"/>
-      <sz val="18"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF005F8C"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF666666"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF888888"/>
       <sz val="9"/>
+      <color rgb="FF999999"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF005F8C"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF005F8C"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF005F8C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="FF666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF999999"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF005F8C"/>
-    </font>
-    <font>
+      <sz val="11"/>
       <color rgb="FFCC0000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="10">
@@ -464,12 +496,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -490,9 +518,6 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -508,6 +533,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,314 +879,328 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF005F8C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5">
-        <v>50</v>
+      <c r="C5" s="3">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="6">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="6">
+        <f>C6*(C8+C9+C10+C11)*C7*52</f>
+        <v>145600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="6">
+        <f>C13*C14*12</f>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="6">
+        <f>C15</f>
         <v>5000</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="8">
-        <f>C6*(C8+C9+C10+C11)*C7*52</f>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="8">
-        <f>C13*C14*12</f>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="8">
-        <f>C15</f>
-      </c>
-    </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="6">
         <f>C12*12</f>
+        <v>2400</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="8">
         <f>C18+C19+C20+C21</f>
+        <v>171000</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="9">
         <v>0.7</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <f>IF(C5&lt;=25,199*12,IF(C5&lt;=100,399*12,IF(C5&lt;=250,699*12,999*12)))</f>
+        <v>4788</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="9">
         <v>0.9</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="9">
         <v>0.85</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="6">
         <f>C18*(1-C25)</f>
+        <v>43680.000000000007</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="6">
         <f>C19*(1-C27)</f>
+        <v>1799.9999999999995</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="6">
         <f>C20*(1-C28)</f>
+        <v>750.00000000000011</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="8">
         <f>C29+C30+C31+C26</f>
+        <v>51018.000000000007</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="11">
         <f>C22-C32</f>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+        <v>119982</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="11">
         <f>C35/12</f>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+        <v>9998.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="12">
         <f>IF(C26&gt;0,(C35/C26)*100,0)</f>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+        <v>2505.8897243107767</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="13">
         <f>IF(C35&gt;0,C26/C35*12,0)</f>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+        <v>0.47887183077461615</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1162,18 +1209,19 @@
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
   </mergeCells>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF005F8C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1182,321 +1230,321 @@
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+    </row>
+    <row r="4" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="18" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="18" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="D8" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="23" t="s">
+      <c r="D9" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="24" t="s">
+      <c r="C11" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="24" t="s">
+      <c r="C12" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="23" t="s">
+      <c r="D13" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="23" t="s">
+      <c r="D14" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="23" t="s">
+      <c r="C15" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="C16" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="18" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="D17" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="23" t="s">
+      <c r="D18" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="23" t="s">
+      <c r="C19" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="18" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1504,6 +1552,7 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A22:E22"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>